--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 16/03/2026 13:06  •  Edição semanal</t>
+          <t>Gerado em: 23/03/2026 13:02  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$57.21</t>
+          <t>$50.60</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-4.70%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$89.51</t>
+          <t>$79.10</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-4.64%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-5.2%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$646.00</t>
+          <t>$627.43</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$204.52</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.73%</t>
+          <t>$198.16</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$56.38</t>
+          <t>$52.09</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-4.78%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1104,9 +1104,9 @@
           <t>$55</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$57.21</t>
+          <t>$50.60</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>-4.70%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$89.51</t>
+          <t>$79.10</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-4.64%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$646.00</t>
+          <t>$627.43</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$204.52</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+0.73%</t>
+          <t>$198.16</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$56.38</t>
+          <t>$52.09</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>-4.78%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$733.71</t>
+          <t>$706.95</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$44.72</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
+          <t>$46.63</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$33.69</t>
+          <t>$36.53</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-3.30%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$180.25</t>
+          <t>$172.70</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$73,994.14</t>
+          <t>$70,753.99</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>+3.29%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>+102.7%</t>
+          <t>+112.0%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,281.06</t>
+          <t>$2,147.92</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+8.05%</t>
+          <t>+2.98%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+163.0%</t>
+          <t>+179.3%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2649,20 +2649,20 @@
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="B3" s="43" t="inlineStr">
         <is>
-          <t>2026-03-16T10:44</t>
+          <t>2026-03-23T10:43</t>
         </is>
       </c>
       <c r="C3" s="43" t="inlineStr">
         <is>
-          <t>📌 TEMA DO DIA: Desaceleração de minerais estratégicos ante recuo de expectativas pré-Summit Trump-Xi; BTC/ETH divergem em flight-to-safety cripto.
-🎯 ATIVO EM DESTAQUE: MP (MP Materials) -4.70% — catalisador negativo: redução de posições antes de negosiações de tarifas em março; Summit é pivô, mas mercado precifica risco de acordo moderado.
-⚠️ VIGIAR HOJE: SCOTUS validou Section 232 (tarifas de segurança nacional); Trump pode usar ferramenta contra minerais chineses em abril, amplificando volatilidade pré-Summit.
-✅ AÇÃO: Reduzir REMX/FCX em 30%; acumular BTC (+2%) como hedge geopolítico até 31/mar; manter dry powder para reposicionar em MP pós-anúncio de acordos comerciais.</t>
+          <t>📌 TEMA DO DIA: Recuo defensivo pré-summit Trump-Xi; mercado precifica risco de escalação tarifária antes das negociações.
+🎯 ATIVO EM DESTAQUE: MP (-4.71%) — queda exagerada ante catalisador de março. Comprador de dips para posição long pré-31/mar, com alvo $65 em cenário dovish de negociação.
+⚠️ VIGIAR HOJE: Comunicado oficial da Casa Branca sobre agenda Trump-Xi. Qualquer sinal de dureza em minerais raros (REMX -4.64%) pode acelerar flight-to-safety em ouro rumo aos $5k JP Morgan.
+✅ AÇÃO: Estabelecer hedge ouro/dólar; mantém posição tática MP com stop em $48. Monitorar Section 232 como gatilho de volatilidade Venezuela (SLB setup).</t>
         </is>
       </c>
     </row>

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,24 +253,21 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -280,7 +277,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 23/03/2026 13:02  •  Edição semanal</t>
+          <t>Gerado em: 30/03/2026 13:14  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$50.60</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-4.71%</t>
+          <t>$51.80</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$79.10</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-4.64%</t>
+          <t>$86.10</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$627.43</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-1.58%</t>
+          <t>$615.84</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1020,9 +1017,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>-1.2%</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$198.16</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-1.28%</t>
+          <t>$189.71</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$52.09</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-2.85%</t>
+          <t>$56.24</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1104,9 +1101,9 @@
           <t>$55</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$50.60</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-4.71%</t>
+          <t>$51.80</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$79.10</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-4.64%</t>
+          <t>$86.10</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1458,260 +1455,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$627.43</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-1.58%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$615.84</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>-1.83%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$198.16</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>-1.28%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$189.71</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-29.4%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-26.2%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$52.09</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>-2.85%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$56.24</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$706.95</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-1.01%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$679.00</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>-12.3%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>-8.7%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$46.63</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>-2.49%</t>
+          <t>$53.50</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>+2.9%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$36.53</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>-1.08%</t>
+          <t>$40.42</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-4.2%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$172.70</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-3.28%</t>
+          <t>$167.52</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>-2.17%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-7.4%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$70,753.99</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+2.87%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>$67,940.59</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>+2.01%</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>+112.0%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+120.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1988,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,147.92</t>
+          <t>$2,074.37</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+2.98%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+179.3%</t>
+          <t>+189.2%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2217,162 +2214,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2438,162 +2435,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2647,76 +2644,76 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
-        <is>
-          <t>23/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="43" t="inlineStr">
-        <is>
-          <t>2026-03-23T10:43</t>
-        </is>
-      </c>
-      <c r="C3" s="43" t="inlineStr">
-        <is>
-          <t>📌 TEMA DO DIA: Recuo defensivo pré-summit Trump-Xi; mercado precifica risco de escalação tarifária antes das negociações.
-🎯 ATIVO EM DESTAQUE: MP (-4.71%) — queda exagerada ante catalisador de março. Comprador de dips para posição long pré-31/mar, com alvo $65 em cenário dovish de negociação.
-⚠️ VIGIAR HOJE: Comunicado oficial da Casa Branca sobre agenda Trump-Xi. Qualquer sinal de dureza em minerais raros (REMX -4.64%) pode acelerar flight-to-safety em ouro rumo aos $5k JP Morgan.
-✅ AÇÃO: Estabelecer hedge ouro/dólar; mantém posição tática MP com stop em $48. Monitorar Section 232 como gatilho de volatilidade Venezuela (SLB setup).</t>
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:38</t>
+        </is>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
+🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
+⚠️ **VIGIAR HOJE:** Comunicado pré-summit Trump sobre agenda chinesa. Sinais de endurecimento aumentariam volatilidade em MP/REMX; acordo prematuro comprimiria minerais raros até nov/2026 (vencimento pausa).
+✅ **AÇÃO:** Reduzir exposição REMX/MP até 30/mar; concentrar em LMT e posições defensivas</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -82,11 +82,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
@@ -95,6 +90,11 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,16 +229,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -265,10 +262,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +715,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 30/03/2026 13:14  •  Edição semanal</t>
+          <t>Gerado em: 06/04/2026 13:04  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +865,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$51.80</t>
+          <t>$49.73</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +890,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
@@ -910,12 +907,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$86.10</t>
+          <t>$88.90</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +932,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -994,12 +991,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$615.84</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>-1.83%</t>
+          <t>$622.79</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1017,9 +1014,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>+0.7%</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1033,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$189.71</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
+          <t>$196.21</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1061,7 +1058,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-28.6%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1075,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$56.24</t>
+          <t>$61.38</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1103,7 +1100,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-10.4%</t>
         </is>
       </c>
     </row>
@@ -1115,35 +1112,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1188,527 +1185,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>$51.80</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+0.19%</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>$49.73</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>+2.73%</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>-13.1%</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>-9.5%</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>$86.10</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+1.77%</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>$88.90</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>-12.9%</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-15.6%</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$615.84</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>-1.83%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>$622.79</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>+0.7%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$189.71</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>$196.21</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>+0.77%</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-26.2%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>-28.6%</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$56.24</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>+0.73%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>$61.38</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>-10.4%</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$679.00</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>$702.50</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>-8.7%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>-11.7%</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1722,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1734,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$53.50</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+2.27%</t>
+          <t>$49.44</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1752,7 +1749,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1774,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1786,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$40.42</t>
+          <t>$38.17</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+4.20%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1826,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1838,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$167.52</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-2.17%</t>
+          <t>$177.39</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1856,7 +1853,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1878,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1923,52 +1920,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$67,940.59</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+2.01%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>$69,442.51</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>+3.90%</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+120.8%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+116.0%</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1982,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +1994,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,074.37</t>
+          <t>$2,144.51</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+5.63%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2009,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+189.2%</t>
+          <t>+179.8%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2031,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2180,196 +2177,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2401,196 +2398,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2620,41 +2617,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2661,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="42" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="42" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="42" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -82,6 +82,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
@@ -90,11 +95,6 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,13 +229,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,10 +265,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -715,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 06/04/2026 13:04  •  Edição semanal</t>
+          <t>Gerado em: 13/04/2026 13:21  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -865,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$49.73</t>
+          <t>$55.24</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -890,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-18.5%</t>
         </is>
       </c>
     </row>
@@ -907,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$88.90</t>
+          <t>$94.50</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -932,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
@@ -991,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$622.79</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+0.83%</t>
+          <t>$613.72</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1014,9 +1017,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$196.21</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.77%</t>
+          <t>$201.56</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1058,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$61.38</t>
+          <t>$67.80</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1100,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
@@ -1112,35 +1115,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1185,527 +1188,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>$49.73</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>+2.73%</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>$55.24</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+2.49%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>-9.5%</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>-18.5%</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>$88.90</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>+0.42%</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>$94.50</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+1.39%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>-15.6%</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>-20.6%</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>$622.79</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>+0.83%</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$613.72</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>$196.21</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>+0.77%</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$201.56</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>-28.6%</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-30.5%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>$61.38</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>+0.29%</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$67.80</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>+2.03%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>-10.4%</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-18.9%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>$702.50</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>+0.79%</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$673.73</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>-2.44%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>-11.7%</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>-8.0%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1722,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1734,10 +1737,10 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$49.44</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+          <t>$51.92</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>-1.18%</t>
         </is>
@@ -1749,7 +1752,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1774,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1786,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$38.17</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+0.45%</t>
+          <t>$37.59</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1801,7 +1804,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1826,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1838,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$177.39</t>
+          <t>$188.63</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1853,7 +1856,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1878,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1920,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>$69,442.51</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>+3.90%</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>$71,166.36</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+116.0%</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+110.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1982,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1994,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,144.51</t>
+          <t>$2,197.02</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2009,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+179.8%</t>
+          <t>+173.1%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2031,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2177,196 +2180,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2398,196 +2401,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2617,41 +2620,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2661,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,21 +253,24 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -277,7 +280,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 13/04/2026 13:21  •  Edição semanal</t>
+          <t>Gerado em: 20/04/2026 13:24  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$55.24</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+2.49%</t>
+          <t>$60.99</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$94.50</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+1.39%</t>
+          <t>$101.63</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-26.2%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$613.72</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
+          <t>$592.19</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+4.7%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$201.56</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>-0.80%</t>
+          <t>$196.42</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$67.80</t>
+          <t>$70.21</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$55.24</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+2.49%</t>
+          <t>$60.99</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$94.50</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+1.39%</t>
+          <t>$101.63</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1455,260 +1458,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$613.72</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$592.19</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-2.52%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>+1.0%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>+4.7%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$201.56</t>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$196.42</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>-0.80%</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-30.5%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-28.7%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$67.80</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>+2.03%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$70.21</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>+2.83%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-18.9%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-21.7%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$673.73</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>-2.44%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$665.26</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>-8.0%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>-6.8%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$51.92</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>-1.18%</t>
+          <t>$52.66</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+1.80%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-7.6%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$37.59</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-0.27%</t>
+          <t>$37.15</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>-6.9%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$188.63</t>
+          <t>$201.68</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-15.2%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$71,166.36</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$75,063.54</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-1.34%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+110.8%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>+99.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,197.02</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
+          <t>$2,313.33</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+173.1%</t>
+          <t>+159.4%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2214,162 +2217,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2435,162 +2438,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2644,17 +2647,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -268,13 +268,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 20/04/2026 13:24  •  Edição semanal</t>
+          <t>Gerado em: 27/04/2026 13:46  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$60.99</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-2.10%</t>
+          <t>$62.22</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-27.7%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$101.63</t>
+          <t>$97.66</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$592.19</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-2.52%</t>
+          <t>$522.62</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+18.6%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$196.42</t>
+          <t>$175.38</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-20.2%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$70.21</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+2.83%</t>
+          <t>$59.82</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$60.99</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-2.10%</t>
+          <t>$62.22</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$101.63</t>
+          <t>$97.66</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$592.19</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-2.52%</t>
+          <t>$522.62</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1545,9 +1545,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>+4.7%</t>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+18.6%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$196.42</t>
+          <t>$175.38</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$70.21</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>+2.83%</t>
+          <t>$59.82</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$665.26</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-1.12%</t>
+          <t>$585.75</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1728,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$52.66</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+1.80%</t>
+          <t>$55.46</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$37.15</t>
+          <t>$40.15</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-2.62%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$201.68</t>
+          <t>$209.24</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$75,063.54</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-1.34%</t>
+          <t>$77,751.93</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1961,9 +1961,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>+99.8%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+92.9%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -1988,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,313.33</t>
+          <t>$2,312.62</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 27/04/2026 13:46  •  Edição semanal</t>
+          <t>Gerado em: 04/05/2026 13:53  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$62.22</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+2.45%</t>
+          <t>$66.21</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-32.0%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$97.66</t>
+          <t>$103.17</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$522.62</t>
+          <t>$519.68</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+18.6%</t>
+          <t>+19.3%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$175.38</t>
+          <t>$175.15</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.1%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$59.82</t>
+          <t>$56.23</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$62.22</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+2.45%</t>
+          <t>$66.21</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$97.66</t>
+          <t>$103.17</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$522.62</t>
+          <t>$519.68</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>+18.6%</t>
+          <t>+19.3%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$175.38</t>
+          <t>$175.15</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$59.82</t>
+          <t>$56.23</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$585.75</t>
+          <t>$574.61</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$55.46</t>
+          <t>$56.41</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$40.15</t>
+          <t>$41.54</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$209.24</t>
+          <t>$199.47</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$77,751.93</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>-0.25%</t>
+          <t>$78,762.05</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>+92.9%</t>
+          <t>+90.4%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,312.62</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-0.95%</t>
+          <t>$2,334.37</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+159.4%</t>
+          <t>+157.0%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,11 +76,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
@@ -95,6 +90,11 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,16 +229,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,16 +250,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -271,16 +265,19 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 04/05/2026 13:53  •  Edição semanal</t>
+          <t>Gerado em: 11/05/2026 14:44  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$66.21</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-0.63%</t>
+          <t>$67.79</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$103.17</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-3.14%</t>
+          <t>$109.95</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-31.8%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$519.68</t>
+          <t>$510.81</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+1.35%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>+21.4%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$175.15</t>
+          <t>$178.60</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$56.23</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
+          <t>$63.75</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+3.41%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-13.7%</t>
         </is>
       </c>
     </row>
@@ -1118,35 +1115,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1191,527 +1188,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>$66.21</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-0.63%</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>$67.79</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>-32.0%</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>-33.6%</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>$103.17</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-3.14%</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>$109.95</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>+3.36%</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>-27.3%</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-31.8%</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$519.68</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>+1.35%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>$510.81</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+19.3%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>+21.4%</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$175.15</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+0.67%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>$178.60</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-20.1%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>-21.6%</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$56.23</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>$63.75</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>+3.41%</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>-13.7%</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$574.61</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>+1.14%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>$552.51</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>+0.54%</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>+7.9%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+          <t>+12.2%</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$56.41</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>-0.90%</t>
+          <t>$53.98</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>-14.9%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$41.54</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>-0.29%</t>
+          <t>$39.89</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-15.7%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$199.47</t>
+          <t>$219.12</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-19.8%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$78,762.05</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>$80,842.46</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+90.4%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>+85.5%</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1988,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,334.37</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+0.49%</t>
+          <t>$2,314.12</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+157.0%</t>
+          <t>+159.3%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2183,196 +2180,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2404,196 +2401,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2623,41 +2620,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2667,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,6 +76,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
@@ -90,11 +95,6 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,13 +229,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,34 +253,34 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 11/05/2026 14:44  •  Edição semanal</t>
+          <t>Gerado em: 18/05/2026 15:26  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$67.79</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+0.53%</t>
+          <t>$55.62</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-9.22%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$109.95</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+3.36%</t>
+          <t>$94.21</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-20.4%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$510.81</t>
+          <t>$519.46</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+21.4%</t>
+          <t>+19.4%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$178.60</t>
+          <t>$173.50</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.3%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$63.75</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+3.41%</t>
+          <t>$61.30</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
@@ -1115,35 +1118,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1188,527 +1191,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>$67.79</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>+0.53%</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>$55.62</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-9.22%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>-33.6%</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>-19.1%</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>$109.95</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>+3.36%</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>$94.21</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-2.44%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>-31.8%</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>-20.4%</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>$510.81</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$519.46</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>+0.67%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>+21.4%</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+19.4%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>$178.60</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>+1.43%</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$173.50</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>-21.6%</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-19.3%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>$63.75</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>+3.41%</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$61.30</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>-2.71%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>-13.7%</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-10.3%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>$552.51</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>+0.54%</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$545.43</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>+12.2%</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+13.7%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$53.98</t>
+          <t>$57.47</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+3.77%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-11.1%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$39.89</t>
+          <t>$42.76</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+2.39%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>-12.3%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$219.12</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+1.82%</t>
+          <t>$222.22</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-27.0%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>$80,842.46</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$76,205.00</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>-2.32%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>+85.5%</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+96.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,314.12</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>-0.73%</t>
+          <t>$2,100.77</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+159.3%</t>
+          <t>+185.6%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2180,196 +2183,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2401,196 +2404,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2620,41 +2623,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,34 +253,31 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 18/05/2026 15:26  •  Edição semanal</t>
+          <t>Gerado em: 25/05/2026 14:49  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$55.62</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-9.22%</t>
+          <t>$64.48</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$94.21</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-2.44%</t>
+          <t>$96.84</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$519.46</t>
+          <t>$533.26</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+2.00%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>+16.3%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$173.50</t>
+          <t>$177.03</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$61.30</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-2.71%</t>
+          <t>$62.01</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$55.62</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-9.22%</t>
+          <t>$64.48</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$94.21</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-2.44%</t>
+          <t>$96.84</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1458,260 +1455,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$519.46</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>+0.67%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$533.26</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>+2.00%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+19.4%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>+16.3%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$173.50</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+1.36%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$177.03</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-19.3%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-20.9%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$61.30</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>-2.71%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$62.01</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>-10.3%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-11.3%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$545.43</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>+0.88%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$555.60</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>+13.7%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>+11.6%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$57.47</t>
+          <t>$57.30</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>-16.5%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$42.76</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+2.39%</t>
+          <t>$41.48</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-18.1%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$222.22</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-1.38%</t>
+          <t>$215.35</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-28.0%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$76,205.00</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>-2.32%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>$77,748.45</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>+1.70%</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+96.8%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>+92.9%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1988,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,100.77</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-3.79%</t>
+          <t>$2,129.17</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+185.6%</t>
+          <t>+181.8%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2217,162 +2214,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2438,162 +2435,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2647,17 +2644,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2667,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,31 +253,34 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 25/05/2026 14:49  •  Edição semanal</t>
+          <t>Gerado em: 01/06/2026 17:32  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$64.48</t>
+          <t>$70.00</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>+8.19%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$96.84</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+1.19%</t>
+          <t>$99.61</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$533.26</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+2.00%</t>
+          <t>$522.31</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+16.3%</t>
+          <t>+18.7%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$177.03</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.60%</t>
+          <t>$176.75</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$62.01</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>-0.48%</t>
+          <t>$67.12</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$64.48</t>
+          <t>$70.00</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>+8.19%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$96.84</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+1.19%</t>
+          <t>$99.61</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1455,260 +1458,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$533.26</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>+2.00%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$522.31</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-1.53%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>+16.3%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>+18.7%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$177.03</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>+0.60%</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$176.75</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-20.9%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-20.8%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$62.01</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$67.12</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>+2.15%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-11.3%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-18.1%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$555.60</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>+0.73%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$543.37</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>-3.60%</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>+11.6%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$57.30</t>
+          <t>$54.59</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-16.2%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$41.48</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-1.14%</t>
+          <t>$39.32</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>-15.6%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$215.35</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-1.90%</t>
+          <t>$221.91</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+5.10%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-25.7%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$77,748.45</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+1.70%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$71,579.16</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-2.83%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>+92.9%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+109.6%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,129.17</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+1.56%</t>
+          <t>$1,988.94</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+181.8%</t>
+          <t>+201.7%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2214,162 +2217,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2435,162 +2438,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2644,17 +2647,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 01/06/2026 17:32  •  Edição semanal</t>
+          <t>Gerado em: 08/06/2026 15:43  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$70.00</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+8.19%</t>
+          <t>$58.63</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-23.2%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$99.61</t>
+          <t>$88.20</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$522.31</t>
+          <t>$518.58</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+19.6%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$176.75</t>
+          <t>$178.88</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-21.7%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$67.12</t>
+          <t>$64.58</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-14.8%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$70.00</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+8.19%</t>
+          <t>$58.63</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$99.61</t>
+          <t>$88.20</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$522.31</t>
+          <t>$518.58</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+19.6%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$176.75</t>
+          <t>$178.88</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$67.12</t>
+          <t>$64.58</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$543.37</t>
+          <t>$534.94</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+15.9%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$54.59</t>
+          <t>$56.70</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$39.32</t>
+          <t>$40.19</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+2.58%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$221.91</t>
+          <t>$208.46</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+5.10%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$71,579.16</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-2.83%</t>
+          <t>$63,859.99</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>+109.6%</t>
+          <t>+134.9%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,988.94</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-0.80%</t>
+          <t>$1,692.97</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+201.7%</t>
+          <t>+254.4%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,24 +253,21 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -280,7 +277,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 08/06/2026 15:43  •  Edição semanal</t>
+          <t>Gerado em: 15/06/2026 17:11  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$58.63</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
+          <t>$59.08</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.8%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$88.20</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-0.44%</t>
+          <t>$97.55</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$518.58</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.99%</t>
+          <t>$532.25</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+16.5%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$178.88</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-1.17%</t>
+          <t>$185.04</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$64.58</t>
+          <t>$69.62</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$58.63</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
+          <t>$59.08</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$88.20</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-0.44%</t>
+          <t>$97.55</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1458,260 +1455,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$518.58</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-0.99%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$532.25</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>-1.50%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>+19.6%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+16.5%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$178.88</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$185.04</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-21.7%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-24.3%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$64.58</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>+1.91%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$69.62</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>+1.77%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>-14.8%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-21.0%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$534.94</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-1.74%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$542.33</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>+15.9%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+14.3%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$56.70</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+3.34%</t>
+          <t>$54.07</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>-15.3%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$40.19</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+2.58%</t>
+          <t>$38.43</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-12.9%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$208.46</t>
+          <t>$212.07</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+1.64%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-23.2%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$63,859.99</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+2.83%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+134.9%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1988,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,692.97</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2013,9 +2010,9 @@
           <t>$6,000</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>+254.4%</t>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2217,162 +2214,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2438,162 +2435,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2647,17 +2644,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2667,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -718,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 15/06/2026 17:11  •  Edição semanal</t>
+          <t>Gerado em: 22/06/2026 16:50  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$59.08</t>
+          <t>$61.56</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-26.9%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$97.55</t>
+          <t>$97.19</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-22.8%</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$532.25</t>
+          <t>$495.48</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+25.1%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$185.04</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.82%</t>
+          <t>$182.58</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$69.62</t>
+          <t>$69.43</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$59.08</t>
+          <t>$61.56</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$97.55</t>
+          <t>$97.19</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>$532.25</t>
+          <t>$495.48</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+25.1%</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>$185.04</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>+0.82%</t>
+          <t>$182.58</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>$69.62</t>
+          <t>$69.43</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>$542.33</t>
+          <t>$507.61</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+22.1%</t>
         </is>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$54.07</t>
+          <t>$47.71</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>-3.76%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$38.43</t>
+          <t>$34.86</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$212.07</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+3.35%</t>
+          <t>$209.78</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$64,612.64</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+132.2%</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,737.16</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2010,9 +2010,9 @@
           <t>$6,000</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>+245.4%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,21 +253,24 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -277,7 +280,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 22/06/2026 16:50  •  Edição semanal</t>
+          <t>Gerado em: 29/06/2026 15:40  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$61.56</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+1.12%</t>
+          <t>$53.18</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$97.19</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
+          <t>$85.54</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$495.48</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>-3.03%</t>
+          <t>$504.84</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+25.1%</t>
+          <t>+22.8%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$182.58</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
+          <t>$187.85</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-25.5%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$69.43</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+1.09%</t>
+          <t>$61.32</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$61.56</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+1.12%</t>
+          <t>$53.18</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$97.19</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
+          <t>$85.54</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1455,260 +1458,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$495.48</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>-3.03%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$504.84</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+25.1%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>+22.8%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$182.58</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>-1.63%</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$187.85</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-23.3%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-25.5%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$69.43</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>+1.09%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$61.32</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>-1.81%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-20.8%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-10.3%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$507.61</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>-2.66%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$496.26</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>+22.1%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>+24.9%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$47.71</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>-0.79%</t>
+          <t>$46.66</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>+0.6%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$34.86</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
+          <t>$34.40</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$209.78</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-0.43%</t>
+          <t>$194.15</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-23.7%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$64,612.64</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+0.70%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$59,796.01</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+132.2%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+150.9%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,737.16</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
+          <t>$1,579.97</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+245.4%</t>
+          <t>+279.8%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2214,162 +2217,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2435,162 +2438,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2644,17 +2647,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 29/06/2026 15:40  •  Edição semanal</t>
+          <t>Gerado em: 06/07/2026 15:25  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$53.18</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-1.34%</t>
+          <t>$53.39</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$85.54</t>
+          <t>$85.10</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$504.84</t>
+          <t>$537.42</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+15.4%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$187.85</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
+          <t>$199.79</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-29.9%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$61.32</t>
+          <t>$60.93</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$53.18</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-1.34%</t>
+          <t>$53.39</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$85.54</t>
+          <t>$85.10</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$504.84</t>
+          <t>$537.42</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+15.4%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$187.85</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
+          <t>$199.79</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$61.32</t>
+          <t>$60.93</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$496.26</t>
+          <t>$543.79</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>+24.9%</t>
+          <t>+14.0%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$46.66</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>-0.72%</t>
+          <t>$46.00</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+4.3%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$34.40</t>
+          <t>$33.42</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.40%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$194.15</t>
+          <t>$195.81</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$59,796.01</t>
+          <t>$62,378.28</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>+150.9%</t>
+          <t>+140.5%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,579.97</t>
+          <t>$1,760.11</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+279.8%</t>
+          <t>+240.9%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 06/07/2026 15:25  •  Edição semanal</t>
+          <t>Gerado em: 13/07/2026 14:27  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$53.39</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
+          <t>$50.71</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$85.10</t>
+          <t>$77.38</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$537.42</t>
+          <t>$519.63</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+15.4%</t>
+          <t>+19.3%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$199.79</t>
+          <t>$196.39</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$60.93</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
+          <t>$61.91</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.2%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$53.39</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
+          <t>$50.71</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$85.10</t>
+          <t>$77.38</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$537.42</t>
+          <t>$519.63</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>+15.4%</t>
+          <t>+19.3%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$199.79</t>
+          <t>$196.39</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$60.93</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
+          <t>$61.91</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$543.79</t>
+          <t>$538.57</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>+14.0%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$46.00</t>
+          <t>$48.14</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$33.42</t>
+          <t>$35.41</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$195.81</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
+          <t>$209.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$62,378.28</t>
+          <t>$62,593.99</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>+140.5%</t>
+          <t>+139.6%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,760.11</t>
+          <t>$1,773.75</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+240.9%</t>
+          <t>+238.3%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -268,13 +268,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 13/07/2026 14:27  •  Edição semanal</t>
+          <t>Gerado em: 20/07/2026 13:59  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$50.71</t>
+          <t>$44.54</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -894,9 +894,9 @@
           <t>$45</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>-11.3%</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$77.38</t>
+          <t>$70.27</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>-3.30%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -936,9 +936,9 @@
           <t>$75</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>-3.1%</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$519.63</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.69%</t>
+          <t>$512.56</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>+21.0%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$196.39</t>
+          <t>$196.53</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.8%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$61.91</t>
+          <t>$59.06</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$50.71</t>
+          <t>$44.54</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$77.38</t>
+          <t>$70.27</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>-3.30%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$519.63</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-0.69%</t>
+          <t>$512.56</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1545,9 +1545,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>+19.3%</t>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+21.0%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$196.39</t>
+          <t>$196.53</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$61.91</t>
+          <t>$59.06</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$538.57</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
+          <t>$526.12</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1701,9 +1701,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>+15.1%</t>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+17.8%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1728,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$48.14</t>
+          <t>$47.08</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$35.41</t>
+          <t>$35.74</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$209.00</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
+          <t>$205.71</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$62,593.99</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-2.19%</t>
+          <t>$64,313.99</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1961,9 +1961,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+139.6%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+133.2%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -1988,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,773.75</t>
+          <t>$1,862.13</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+238.3%</t>
+          <t>+222.2%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,34 +253,31 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 20/07/2026 13:59  •  Edição semanal</t>
+          <t>Gerado em: 27/07/2026 14:26  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$44.54</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-1.55%</t>
+          <t>$41.97</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+7.2%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$70.27</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-3.30%</t>
+          <t>$68.15</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+10.1%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$512.56</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+0.74%</t>
+          <t>$582.30</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+21.0%</t>
+          <t>+6.5%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$196.53</t>
+          <t>$217.78</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$59.06</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+1.16%</t>
+          <t>$62.22</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$44.54</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-1.55%</t>
+          <t>$41.97</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$70.27</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-3.30%</t>
+          <t>$68.15</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1441,9 +1438,9 @@
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>+6.7%</t>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>+10.1%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1458,260 +1455,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$512.56</t>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$582.30</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>+0.74%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+21.0%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>+6.5%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$196.53</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+1.56%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$217.78</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>+2.35%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-28.8%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-35.7%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$59.06</t>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$62.22</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>+1.16%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+          <t>-0.61%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>-6.9%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$526.12</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>+0.87%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$549.51</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>+1.34%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>+17.8%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+          <t>+12.8%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$47.08</t>
+          <t>$52.42</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>+2.0%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$35.74</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
+          <t>$32.89</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-2.1%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>+6.4%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$205.71</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+1.43%</t>
+          <t>$200.15</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-22.2%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$64,313.99</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>-0.26%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>$65,012.01</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>+133.2%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+          <t>+130.7%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,862.13</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
+          <t>$1,946.20</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+2.80%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+222.2%</t>
+          <t>+208.3%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2217,162 +2214,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2438,162 +2435,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2647,17 +2644,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2667,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -82,11 +82,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
@@ -95,6 +90,11 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,16 +229,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -265,13 +262,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +715,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 27/07/2026 14:26  •  Edição semanal</t>
+          <t>Gerado em: 03/08/2026 14:31  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +865,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$41.97</t>
+          <t>$43.19</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>+4.40%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +890,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>+4.2%</t>
         </is>
       </c>
     </row>
@@ -910,12 +907,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$68.15</t>
+          <t>$67.08</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +932,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+10.1%</t>
+          <t>+11.8%</t>
         </is>
       </c>
     </row>
@@ -994,12 +991,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$582.30</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
+          <t>$588.22</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1019,7 +1016,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+6.5%</t>
+          <t>+5.4%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1033,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$217.78</t>
+          <t>$217.93</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1061,7 +1058,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-35.8%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1075,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$62.22</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>-0.61%</t>
+          <t>$62.76</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1103,7 +1100,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
     </row>
@@ -1115,35 +1112,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1188,527 +1185,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>$41.97</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+1.62%</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>$43.19</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>+4.40%</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>+7.2%</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>$68.15</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+0.95%</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>$67.08</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>+1.68%</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>+10.1%</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>+11.8%</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$582.30</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>$588.22</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>+0.94%</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>+6.5%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$217.78</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>+2.35%</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>$217.93</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>+1.26%</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-35.7%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>-35.8%</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$62.22</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>-0.61%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>$62.76</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-11.6%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>-12.4%</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$549.51</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>+1.34%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>$553.38</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>+2.01%</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>+12.8%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>+12.0%</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1722,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1734,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$52.42</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>$49.57</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1752,7 +1749,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1774,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1786,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$32.89</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-1.41%</t>
+          <t>$31.87</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>+6.4%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1826,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1838,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$200.15</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-3.23%</t>
+          <t>$204.99</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1856,7 +1853,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1878,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1923,52 +1920,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$65,012.01</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+0.55%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>$63,859.99</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>+1.19%</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+130.7%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>+134.9%</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1982,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +1994,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,946.20</t>
+          <t>$1,869.20</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+2.80%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2009,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+208.3%</t>
+          <t>+221.0%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2031,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2180,196 +2177,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2401,196 +2398,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2620,41 +2617,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2661,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="42" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="42" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="42" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -82,6 +82,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
@@ -90,11 +95,6 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,13 +229,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,13 +265,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -715,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 03/08/2026 14:31  •  Edição semanal</t>
+          <t>Gerado em: 10/08/2026 12:59  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -865,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$43.19</t>
+          <t>$51.11</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+4.40%</t>
+          <t>+7.62%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -888,9 +891,9 @@
           <t>$45</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>+4.2%</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>-12.0%</t>
         </is>
       </c>
     </row>
@@ -907,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$67.08</t>
+          <t>$77.04</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>+4.93%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -930,9 +933,9 @@
           <t>$75</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>+11.8%</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -991,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$588.22</t>
+          <t>$587.95</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1016,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+5.5%</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$217.93</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+1.26%</t>
+          <t>$223.03</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1058,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$62.76</t>
+          <t>$69.62</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1100,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
@@ -1112,35 +1115,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1185,527 +1188,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>$43.19</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>+4.40%</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>$51.11</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+7.62%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>+4.2%</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>-12.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>$67.08</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>+1.68%</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>$77.04</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+4.93%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>+11.8%</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>$588.22</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>+0.94%</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>$587.95</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>+5.4%</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>$217.93</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>+1.26%</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>$223.03</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>-35.8%</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>-37.2%</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>$62.76</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>$69.62</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>+2.11%</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>-12.4%</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>-21.0%</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>$553.38</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>+2.01%</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>$571.58</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>+0.68%</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>+12.0%</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>+8.5%</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1722,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1734,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$49.57</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
+          <t>$50.53</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1749,7 +1752,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1774,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1786,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$31.87</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>-1.18%</t>
+          <t>$31.89</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1826,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1838,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$204.99</t>
+          <t>$223.96</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+2.11%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1853,7 +1856,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1878,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1920,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>$63,859.99</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>+1.19%</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>$64,888.01</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>+134.9%</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+131.2%</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1982,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1994,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,869.20</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+0.66%</t>
+          <t>$1,906.29</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2009,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+221.0%</t>
+          <t>+214.7%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2031,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2177,196 +2180,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2398,196 +2401,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2617,41 +2620,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2661,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -718,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 10/08/2026 12:59  •  Edição semanal</t>
+          <t>Gerado em: 17/08/2026 12:36  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$51.11</t>
+          <t>$58.74</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+7.62%</t>
+          <t>+5.53%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-23.4%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$77.04</t>
+          <t>$78.55</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+4.93%</t>
+          <t>+3.18%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$587.95</t>
+          <t>$608.68</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+1.9%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$223.03</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
+          <t>$222.97</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$69.62</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+2.11%</t>
+          <t>$66.49</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$51.11</t>
+          <t>$58.74</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>+7.62%</t>
+          <t>+5.53%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$77.04</t>
+          <t>$78.55</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>+4.93%</t>
+          <t>+3.18%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>$587.95</t>
+          <t>$608.68</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+1.9%</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>$223.03</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
+          <t>$222.97</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>$69.62</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>+2.11%</t>
+          <t>$66.49</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>$571.58</t>
+          <t>$585.87</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>+8.5%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$50.53</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>-1.96%</t>
+          <t>$53.77</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$31.89</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-1.91%</t>
+          <t>$34.42</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+4.81%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>+9.8%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$223.96</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+2.27%</t>
+          <t>$225.16</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>$64,888.01</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
+          <t>$63,611.32</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>+131.2%</t>
+          <t>+135.8%</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,906.29</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>-0.60%</t>
+          <t>$1,900.35</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+214.7%</t>
+          <t>+215.7%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
